--- a/store/麦安研产品销售周度排行_格式化模板.xlsx
+++ b/store/麦安研产品销售周度排行_格式化模板.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wadec\Documents\projects\mainyan-auto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wadec\Documents\projects\mainyan-auto\store\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25FF4040-9AFA-414E-951B-F66C1BC272C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F597686D-C32E-47B1-A341-C6A099042260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="15552" windowHeight="16656" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="宝泰6月-1" sheetId="2" r:id="rId1"/>
@@ -153,7 +153,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -175,6 +175,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -209,7 +215,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -268,13 +274,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="4" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -634,9 +634,9 @@
         <v>0</v>
       </c>
       <c r="G3" s="5"/>
-      <c r="H3" s="4" t="e">
-        <f>G3/(G3+D3)</f>
-        <v>#DIV/0!</v>
+      <c r="H3" s="4" t="str">
+        <f>IF(G3=0,"",G3/(G3+D3))</f>
+        <v/>
       </c>
       <c r="I3" s="2"/>
     </row>
@@ -657,9 +657,9 @@
         <v>0</v>
       </c>
       <c r="G4" s="5"/>
-      <c r="H4" s="4" t="e">
-        <f t="shared" ref="H4:H10" si="1">G4/(G4+D4)</f>
-        <v>#DIV/0!</v>
+      <c r="H4" s="4" t="str">
+        <f t="shared" ref="H4:H10" si="1">IF(G4=0,"",G4/(G4+D4))</f>
+        <v/>
       </c>
       <c r="I4" s="2"/>
     </row>
@@ -680,9 +680,9 @@
         <v>0</v>
       </c>
       <c r="G5" s="8"/>
-      <c r="H5" s="9" t="e">
+      <c r="H5" s="9" t="str">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v/>
       </c>
       <c r="I5" s="6"/>
     </row>
@@ -703,9 +703,9 @@
         <v>0</v>
       </c>
       <c r="G6" s="8"/>
-      <c r="H6" s="9" t="e">
+      <c r="H6" s="9" t="str">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v/>
       </c>
       <c r="I6" s="6"/>
     </row>
@@ -726,9 +726,9 @@
         <v>0</v>
       </c>
       <c r="G7" s="12"/>
-      <c r="H7" s="13" t="e">
+      <c r="H7" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v/>
       </c>
       <c r="I7" s="10"/>
     </row>
@@ -749,9 +749,9 @@
         <v>0</v>
       </c>
       <c r="G8" s="12"/>
-      <c r="H8" s="13" t="e">
+      <c r="H8" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v/>
       </c>
       <c r="I8" s="10"/>
     </row>
@@ -767,14 +767,14 @@
       </c>
       <c r="D9" s="14"/>
       <c r="E9" s="15"/>
-      <c r="F9" s="20">
+      <c r="F9" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G9" s="21"/>
-      <c r="H9" s="22" t="e">
+      <c r="G9" s="15"/>
+      <c r="H9" s="20" t="str">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v/>
       </c>
       <c r="I9" s="1"/>
     </row>
@@ -790,14 +790,14 @@
       </c>
       <c r="D10" s="14"/>
       <c r="E10" s="1"/>
-      <c r="F10" s="20">
+      <c r="F10" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G10" s="21"/>
-      <c r="H10" s="22" t="e">
+      <c r="G10" s="15"/>
+      <c r="H10" s="20" t="str">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v/>
       </c>
       <c r="I10" s="1"/>
     </row>
